--- a/assets/舜斯-专审文件/舜斯--RD、PS规划表.xlsx
+++ b/assets/舜斯-专审文件/舜斯--RD、PS规划表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/swh/project_launch/assets/舜斯-专审文件/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D21800-1AC3-AC40-9978-AB83C9FA02D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F882F32F-490A-F54F-8426-152720124289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="27940" windowHeight="12380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2600" yWindow="900" windowWidth="27940" windowHeight="12380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RD、PS表" sheetId="1" r:id="rId1"/>
@@ -339,14 +339,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -641,14 +641,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.5" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="27.5" customHeight="1">
@@ -684,7 +684,7 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="27.5" customHeight="1">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -707,7 +707,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="64" customHeight="1">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
@@ -728,7 +728,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="61" customHeight="1">
-      <c r="A6" s="12"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
@@ -749,7 +749,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="71" customHeight="1">
-      <c r="A7" s="12"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
@@ -770,7 +770,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="79" customHeight="1">
-      <c r="A8" s="12"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
@@ -791,7 +791,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="68" customHeight="1">
-      <c r="A9" s="12"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
@@ -812,7 +812,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="67" customHeight="1">
-      <c r="A10" s="12"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
@@ -833,7 +833,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="108" customHeight="1">
-      <c r="A11" s="12"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="4" t="s">
         <v>31</v>
       </c>
@@ -854,7 +854,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="80" customHeight="1">
-      <c r="A12" s="12"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="4" t="s">
         <v>33</v>
       </c>
@@ -892,14 +892,14 @@
       <c r="D18" s="10"/>
     </row>
     <row r="25" spans="3:11" ht="19">
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="3:11" ht="19">
@@ -935,7 +935,7 @@
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="3:11" ht="17">
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -958,7 +958,7 @@
       </c>
     </row>
     <row r="29" spans="3:11" ht="409.6">
-      <c r="C29" s="12"/>
+      <c r="C29" s="13"/>
       <c r="D29" s="4" t="s">
         <v>19</v>
       </c>
@@ -977,12 +977,12 @@
       <c r="I29" s="8">
         <v>0.42</v>
       </c>
-      <c r="K29" s="13" t="s">
+      <c r="K29" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="30" spans="3:11" ht="112">
-      <c r="C30" s="12"/>
+      <c r="C30" s="13"/>
       <c r="D30" s="4" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1003,7 @@
       </c>
     </row>
     <row r="31" spans="3:11" ht="112">
-      <c r="C31" s="12"/>
+      <c r="C31" s="13"/>
       <c r="D31" s="4" t="s">
         <v>23</v>
       </c>
